--- a/data_input/input_crop_TSUM_parameters_TOGO_HI.xlsx
+++ b/data_input/input_crop_TSUM_parameters_TOGO_HI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Spiller\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB5D04C-72F1-44D2-A9A8-82FDB6F740E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81439259-34F8-49FB-B8F6-CC1FDFABFDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11835" xr2:uid="{0EBC9278-16C4-4F19-BFBC-BE9217943952}"/>
+    <workbookView xWindow="1890" yWindow="8100" windowWidth="21600" windowHeight="13185" xr2:uid="{0EBC9278-16C4-4F19-BFBC-BE9217943952}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
   <si>
     <t>Crop_name</t>
   </si>
@@ -167,7 +167,25 @@
     <t>sugarcane</t>
   </si>
   <si>
-    <t>low</t>
+    <t>SDG</t>
+  </si>
+  <si>
+    <t>HB_flag</t>
+  </si>
+  <si>
+    <t>cassava</t>
+  </si>
+  <si>
+    <t>cocoa</t>
+  </si>
+  <si>
+    <t>coffee</t>
+  </si>
+  <si>
+    <t>cashew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -177,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +207,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -216,8 +240,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,167 +556,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C5A6A-0B2F-4690-8ED4-94CA56D6CD01}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" customWidth="1"/>
-    <col min="28" max="28" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.28515625" customWidth="1"/>
+    <col min="28" max="28" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.42578125" customWidth="1"/>
+    <col min="30" max="30" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
       <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>20</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>13</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>0.45</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>135</v>
       </c>
-      <c r="H2">
-        <f>G2*0.8</f>
+      <c r="I2">
+        <f>H2*0.8</f>
         <v>108</v>
       </c>
-      <c r="I2" s="2">
-        <f>G2*1.1</f>
+      <c r="J2" s="2">
+        <f>H2*1.1</f>
         <v>148.5</v>
-      </c>
-      <c r="J2" s="1">
-        <v>3</v>
       </c>
       <c r="K2">
         <v>0.3</v>
@@ -701,115 +732,121 @@
         <v>1</v>
       </c>
       <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
         <v>15</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>30</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>40</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>15</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>0.3</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>1.2</v>
       </c>
-      <c r="S2" s="1">
+      <c r="T2" s="1">
         <v>0.35</v>
       </c>
-      <c r="T2" s="1">
+      <c r="U2" s="1">
         <v>0.85</v>
-      </c>
-      <c r="U2" s="1">
-        <v>0.4</v>
       </c>
       <c r="V2" s="1">
         <v>0.4</v>
       </c>
       <c r="W2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="X2" s="1">
         <v>1.5</v>
       </c>
-      <c r="X2" s="1">
+      <c r="Y2" s="1">
         <v>0.2</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="Z2" s="1">
         <v>1.25</v>
       </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
       <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>15</v>
       </c>
-      <c r="AB2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>26</v>
-      </c>
       <c r="AD2" t="s">
         <v>26</v>
       </c>
       <c r="AE2" t="s">
         <v>26</v>
       </c>
-      <c r="AF2">
-        <f t="shared" ref="AF2:AF3" si="0">AG2*0.95</f>
+      <c r="AF2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AH3" si="0">AI2*0.95</f>
         <v>2422.5</v>
       </c>
-      <c r="AG2">
+      <c r="AI2">
         <v>2550</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2">
         <v>2750</v>
       </c>
-      <c r="AI2">
+      <c r="AK2">
         <v>4725</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>5400</v>
       </c>
-      <c r="AK2">
-        <f t="shared" ref="AK2:AK3" si="1">1.05*AJ2</f>
+      <c r="AM2">
+        <f t="shared" ref="AM2:AM3" si="1">1.05*AL2</f>
         <v>5670</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>0.5</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>6.5</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>135</v>
       </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H4" si="2">G3*0.8</f>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="2">H3*0.8</f>
         <v>108</v>
       </c>
-      <c r="I3" s="2">
-        <f t="shared" ref="I3:I4" si="3">G3*1.1</f>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J4" si="3">H3*1.1</f>
         <v>148.5</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.9</v>
       </c>
       <c r="K3">
         <v>0.3</v>
@@ -818,116 +855,122 @@
         <v>1</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
         <v>15</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>20</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>45</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>20</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>1.05</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>1.2</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <v>0.9</v>
       </c>
-      <c r="T3" s="1">
+      <c r="U3" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="U3" s="1">
-        <v>1</v>
-      </c>
       <c r="V3" s="1">
         <v>1</v>
       </c>
       <c r="W3" s="1">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1">
         <v>2.5</v>
       </c>
-      <c r="X3" s="1">
+      <c r="Y3" s="1">
         <v>0.2</v>
       </c>
-      <c r="Y3" s="1">
+      <c r="Z3" s="1">
         <v>2</v>
       </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
       <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>15</v>
       </c>
-      <c r="AB3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>26</v>
-      </c>
       <c r="AD3" t="s">
         <v>26</v>
       </c>
       <c r="AE3" t="s">
         <v>26</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH3">
         <f t="shared" si="0"/>
         <v>2636.25</v>
       </c>
-      <c r="AG3">
+      <c r="AI3">
         <v>2775</v>
       </c>
-      <c r="AH3">
+      <c r="AJ3">
         <v>2887.5</v>
       </c>
-      <c r="AI3">
+      <c r="AK3">
         <v>3750</v>
       </c>
-      <c r="AJ3">
+      <c r="AL3">
         <v>4050</v>
       </c>
-      <c r="AK3">
+      <c r="AM3">
         <f t="shared" si="1"/>
         <v>4252.5</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>0.36</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>4.5</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>135</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <f t="shared" si="3"/>
         <v>148.5</v>
       </c>
-      <c r="J4" s="1">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="K4">
         <v>0.3</v>
       </c>
@@ -935,195 +978,714 @@
         <v>1</v>
       </c>
       <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>25</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>50</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>15</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>0.4</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <v>0.5</v>
       </c>
-      <c r="T4" s="1">
+      <c r="U4" s="1">
         <v>0.85</v>
-      </c>
-      <c r="U4" s="1">
-        <v>0.2</v>
       </c>
       <c r="V4" s="1">
         <v>0.2</v>
       </c>
       <c r="W4" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="X4" s="1">
         <v>0.8</v>
       </c>
-      <c r="X4" s="1">
+      <c r="Y4" s="1">
         <v>0.2</v>
       </c>
-      <c r="Y4" s="1">
+      <c r="Z4" s="1">
         <v>0.85</v>
       </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
       <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>12.5</v>
       </c>
-      <c r="AB4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>26</v>
-      </c>
       <c r="AD4" t="s">
         <v>26</v>
       </c>
       <c r="AE4" t="s">
         <v>26</v>
       </c>
-      <c r="AF4">
-        <f>AG4*0.95</f>
+      <c r="AF4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH4">
+        <f>AI4*0.95</f>
         <v>2565</v>
       </c>
-      <c r="AG4">
+      <c r="AI4">
         <v>2700</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4">
         <v>2850</v>
       </c>
-      <c r="AI4">
+      <c r="AK4">
         <v>3850</v>
       </c>
-      <c r="AJ4">
+      <c r="AL4">
         <v>4200</v>
       </c>
-      <c r="AK4">
-        <f>1.05*AJ4</f>
+      <c r="AM4">
+        <f>1.05*AL4</f>
         <v>4410</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <v>0.25</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>330</v>
+      </c>
+      <c r="I5">
+        <v>150</v>
+      </c>
+      <c r="J5">
+        <v>360</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5">
+        <v>30</v>
+      </c>
+      <c r="R5">
+        <v>0.4</v>
+      </c>
+      <c r="S5">
+        <v>1.25</v>
+      </c>
+      <c r="T5">
+        <v>0.75</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z5">
+        <v>1.2</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>70</v>
+      </c>
+      <c r="AE5">
+        <v>200</v>
+      </c>
+      <c r="AF5">
+        <v>120</v>
+      </c>
+      <c r="AG5">
+        <v>180</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" ref="AH5:AH9" si="4">AI5*0.95</f>
+        <v>5700</v>
+      </c>
+      <c r="AI5">
+        <v>6000</v>
+      </c>
+      <c r="AJ5">
+        <v>6750</v>
+      </c>
+      <c r="AK5">
+        <v>10000</v>
+      </c>
+      <c r="AL5">
+        <v>10950</v>
+      </c>
+      <c r="AM5">
+        <f>1.05*AL5</f>
+        <v>11497.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>270</v>
+      </c>
+      <c r="I6">
+        <f>H6*0.8</f>
+        <v>216</v>
+      </c>
+      <c r="J6">
+        <f>H6*1.1</f>
+        <v>297</v>
+      </c>
+      <c r="K6">
+        <v>0.45</v>
+      </c>
+      <c r="L6">
+        <v>1.75</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N6">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>35</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6">
+        <v>20</v>
+      </c>
+      <c r="R6">
+        <v>0.3</v>
+      </c>
+      <c r="S6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T6">
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6" t="s">
+        <v>26</v>
+      </c>
+      <c r="W6" t="s">
+        <v>26</v>
+      </c>
+      <c r="X6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>10</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>240</v>
+      </c>
+      <c r="AF6">
+        <v>60</v>
+      </c>
+      <c r="AG6">
+        <v>120</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="4"/>
+        <v>6175</v>
+      </c>
+      <c r="AI6">
+        <v>6500</v>
+      </c>
+      <c r="AJ6">
+        <v>7500</v>
+      </c>
+      <c r="AK6">
+        <v>10950</v>
+      </c>
+      <c r="AL6">
+        <v>12775</v>
+      </c>
+      <c r="AM6">
+        <f>1.05*AL6</f>
+        <v>13413.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+      <c r="I7">
+        <f>H7*0.8</f>
+        <v>240</v>
+      </c>
+      <c r="J7" s="2">
+        <f>H7*1.1</f>
+        <v>330</v>
+      </c>
+      <c r="K7">
+        <v>0.4</v>
+      </c>
+      <c r="L7">
+        <v>1.75</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>30</v>
+      </c>
+      <c r="P7">
+        <v>40</v>
+      </c>
+      <c r="Q7">
+        <v>15</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="U7" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="V7" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7" t="s">
+        <v>26</v>
+      </c>
+      <c r="X7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>270</v>
+      </c>
+      <c r="AF7">
+        <v>120</v>
+      </c>
+      <c r="AG7">
+        <v>150</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="4"/>
+        <v>7362.5</v>
+      </c>
+      <c r="AI7">
+        <v>7750</v>
+      </c>
+      <c r="AJ7">
+        <v>8500</v>
+      </c>
+      <c r="AK7">
+        <v>9750</v>
+      </c>
+      <c r="AL7">
+        <v>10950</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" ref="AM7:AM9" si="5">1.05*AL7</f>
+        <v>11497.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>270</v>
+      </c>
+      <c r="I8">
+        <f>H8*0.8</f>
+        <v>216</v>
+      </c>
+      <c r="J8" s="2">
+        <f>H8*1.1</f>
+        <v>297</v>
+      </c>
+      <c r="K8">
+        <v>0.4</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>2.5</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>30</v>
+      </c>
+      <c r="P8">
+        <v>40</v>
+      </c>
+      <c r="Q8">
+        <v>20</v>
+      </c>
+      <c r="R8">
+        <v>1.05</v>
+      </c>
+      <c r="S8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="V8" t="s">
+        <v>26</v>
+      </c>
+      <c r="W8" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>270</v>
+      </c>
+      <c r="AF8">
+        <v>90</v>
+      </c>
+      <c r="AG8">
+        <v>180</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="4"/>
+        <v>6887.5</v>
+      </c>
+      <c r="AI8">
+        <v>7250</v>
+      </c>
+      <c r="AJ8">
+        <v>8000</v>
+      </c>
+      <c r="AK8">
+        <v>10950</v>
+      </c>
+      <c r="AL8">
+        <v>12775</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="5"/>
+        <v>13413.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="1">
         <v>3.5</v>
       </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>330</v>
-      </c>
-      <c r="H5" s="4">
-        <v>150</v>
-      </c>
-      <c r="I5" s="4">
-        <v>360</v>
-      </c>
-      <c r="J5" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="K5" s="4">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="L5" s="4">
-        <v>2</v>
-      </c>
-      <c r="M5" s="4">
+      <c r="H9">
+        <v>180</v>
+      </c>
+      <c r="I9">
+        <f>H9*0.8</f>
+        <v>144</v>
+      </c>
+      <c r="J9" s="2">
+        <f>H9*1.1</f>
+        <v>198.00000000000003</v>
+      </c>
+      <c r="K9">
+        <v>0.5</v>
+      </c>
+      <c r="L9">
+        <f>(1.5+1.5/2)</f>
+        <v>2.25</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>25</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <v>0.8</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>0.8</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="V9" t="s">
+        <v>26</v>
+      </c>
+      <c r="W9" t="s">
+        <v>26</v>
+      </c>
+      <c r="X9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z9">
+        <v>0.9</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
         <v>10</v>
       </c>
-      <c r="N5" s="4">
-        <v>15</v>
-      </c>
-      <c r="O5" s="4">
-        <v>45</v>
-      </c>
-      <c r="P5" s="4">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="R5" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="S5" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="T5" s="4">
-        <v>1</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>70</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>200</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>120</v>
-      </c>
-      <c r="AE5" s="4">
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>270</v>
+      </c>
+      <c r="AF9">
+        <v>90</v>
+      </c>
+      <c r="AG9">
         <v>180</v>
       </c>
-      <c r="AF5" s="4">
-        <v>5700</v>
-      </c>
-      <c r="AG5" s="4">
-        <v>6000</v>
-      </c>
-      <c r="AH5" s="4">
-        <v>6750</v>
-      </c>
-      <c r="AI5" s="4">
-        <v>11498</v>
-      </c>
-      <c r="AJ5" s="4">
+      <c r="AH9">
+        <f t="shared" si="4"/>
+        <v>8312.5</v>
+      </c>
+      <c r="AI9">
+        <v>8750</v>
+      </c>
+      <c r="AJ9">
+        <v>7000</v>
+      </c>
+      <c r="AK9">
         <v>10950</v>
       </c>
-      <c r="AK5" s="4">
-        <v>10000</v>
-      </c>
+      <c r="AL9">
+        <v>12775</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="5"/>
+        <v>13413.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="K13" s="4"/>
+      <c r="AI13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="K14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
